--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484059_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484059_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H. OLAGUIBE GONZALEZ</t>
+          <t>O. JIMENEZ ROCA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3369</v>
+        <v>-0.1795</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2898</v>
+        <v>-0.1247</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9529</v>
+        <v>-0.0548</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1304</v>
+        <v>-0.0591</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4788</v>
+        <v>-0.2016</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3485</v>
+        <v>0.1425</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7439</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5807</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1632</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6135</v>
+        <v>-0.0591</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1018</v>
+        <v>-0.2016</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5117</v>
+        <v>0.1425</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1903</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1507</v>
+        <v>-0.1205</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4739</v>
+        <v>-0.1247</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3232</v>
+        <v>0.0042</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.9522</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7458</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.08</v>
+        <v>-0.5723</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.3303</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8184</v>
+        <v>-0.9026</v>
       </c>
       <c r="G3" t="n">
         <v>0.791</v>
@@ -688,13 +688,13 @@
         <v>0.5952</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0062</v>
+        <v>-0.486</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4308</v>
+        <v>0.0227</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4246</v>
+        <v>-0.5087</v>
       </c>
       <c r="V3" t="n">
         <v>-1.4724</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. JIMENEZ ROCA</t>
+          <t>H. OLAGUIBE GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2637</v>
+        <v>-0.9045</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1247</v>
+        <v>0.0484</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.139</v>
+        <v>-0.9529</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0591</v>
+        <v>2.1304</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2016</v>
+        <v>2.4788</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1425</v>
+        <v>-0.3485</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2.7439</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2.5807</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.1632</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0591</v>
+        <v>-0.6135</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2016</v>
+        <v>-0.1018</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1425</v>
+        <v>-0.5117</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.1822</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.1903</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2046</v>
+        <v>-0.0907</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1247</v>
+        <v>0.2325</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0799</v>
+        <v>-0.3232</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.9522</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.7458</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. MARTÍN LLAVERÍA</t>
+          <t>P. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.132</v>
+        <v>-0.9588</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4474</v>
+        <v>-0.6364</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3154</v>
+        <v>-0.3224</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0993</v>
+        <v>-0.6995</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5034</v>
+        <v>0.0299</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5959</v>
+        <v>-0.7294</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9784</v>
+        <v>-0.5797</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4085</v>
+        <v>0.0202</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5699</v>
+        <v>-0.5999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1209</v>
+        <v>-0.1198</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0949</v>
+        <v>0.0098</v>
       </c>
       <c r="O5" t="n">
-        <v>0.026</v>
+        <v>-0.1295</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5952</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3887</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4297</v>
+        <v>-0.3982</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.442</v>
+        <v>0.1417</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0123</v>
+        <v>-0.5399</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2065</v>
+        <v>0.3373</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2065</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. MORENO MARTIN</t>
+          <t>L. MARTÍN LLAVERÍA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.247</v>
+        <v>-1.2153</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8404</v>
+        <v>-1.3624</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4066</v>
+        <v>0.1471</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6995</v>
+        <v>1.0993</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0299</v>
+        <v>0.5034</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7294</v>
+        <v>0.5959</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5797</v>
+        <v>0.9784</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0202</v>
+        <v>0.4085</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5999</v>
+        <v>0.5699</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1198</v>
+        <v>0.1209</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0098</v>
+        <v>0.0949</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1295</v>
+        <v>0.026</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1984</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1984</v>
+        <v>-1.9838</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6864</v>
+        <v>-0.513</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0623</v>
+        <v>-0.357</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6241</v>
+        <v>-0.156</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3373</v>
+        <v>-1.2065</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3373</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5395</v>
+        <v>-1.6356</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.4553</v>
+        <v>-2.9622</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9158</v>
+        <v>1.3266</v>
       </c>
       <c r="G7" t="n">
         <v>0.5599</v>
@@ -1000,13 +1000,13 @@
         <v>0.9919</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3816</v>
+        <v>-0.4776</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0485</v>
+        <v>-0.5554</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6669</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>0.266</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.638</v>
+        <v>-2.0002</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6452</v>
+        <v>-1.9513</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0072</v>
+        <v>-0.0489</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6516</v>
@@ -1078,13 +1078,13 @@
         <v>0.3968</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1848</v>
+        <v>-0.547</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4932</v>
+        <v>0.1871</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.678</v>
+        <v>-0.7341</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7177</v>
+        <v>-2.3773</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4947</v>
+        <v>-2.1262</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.223</v>
+        <v>-0.2511</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9398</v>
@@ -1156,13 +1156,13 @@
         <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.107</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8615</v>
+        <v>-0.4931</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2455</v>
+        <v>-0.2736</v>
       </c>
       <c r="V9" t="n">
         <v>-0.266</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.5292</v>
+        <v>-4.7937</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.2986</v>
+        <v>-4.7034</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2306</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5652</v>
@@ -1234,13 +1234,13 @@
         <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1705</v>
+        <v>-0.4351</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1732</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0027</v>
+        <v>0.143</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6638</v>
+        <v>-4.9128</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2972</v>
+        <v>-1.8267</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3666</v>
+        <v>-3.0861</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0929</v>
@@ -1312,13 +1312,13 @@
         <v>1.1903</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.3806</v>
+        <v>-1.6296</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7991</v>
+        <v>-0.3287</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5815</v>
+        <v>-1.3009</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2065</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.0478</v>
+        <v>-6.0366</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8514</v>
+        <v>-3.1769</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1964</v>
+        <v>-2.8598</v>
       </c>
       <c r="G12" t="n">
         <v>1.8368</v>
@@ -1390,13 +1390,13 @@
         <v>1.3887</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4055</v>
+        <v>-1.3944</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8615</v>
+        <v>-0.187</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5441</v>
+        <v>-1.2074</v>
       </c>
       <c r="V12" t="n">
         <v>0.266</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-26.5218</v>
+        <v>-25.5866</v>
       </c>
       <c r="E13" t="n">
-        <v>-19.4267</v>
+        <v>-18.4915</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.0951</v>
+        <v>-7.0952</v>
       </c>
       <c r="G13" t="n">
         <v>-1.590700000000001</v>
@@ -1438,7 +1438,7 @@
         <v>-0.2301999999999995</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.360499999999999</v>
+        <v>-1.3605</v>
       </c>
       <c r="J13" t="n">
         <v>4.715199999999999</v>
@@ -1453,7 +1453,7 @@
         <v>-6.3057</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.5331</v>
+        <v>-6.533099999999999</v>
       </c>
       <c r="O13" t="n">
         <v>0.2274</v>
@@ -1468,13 +1468,13 @@
         <v>9.9193</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.793799999999999</v>
+        <v>-6.8587</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.9749</v>
+        <v>-2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.819</v>
+        <v>-4.8188</v>
       </c>
       <c r="V13" t="n">
         <v>-5.2343</v>
@@ -1483,7 +1483,7 @@
         <v>0.6554</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.8898</v>
+        <v>-5.889799999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9778</v>
+        <v>6.5977</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7331</v>
+        <v>3.325</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2447</v>
+        <v>3.2728</v>
       </c>
       <c r="G14" t="n">
         <v>1.7286</v>
@@ -1546,13 +1546,13 @@
         <v>1.9838</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1184</v>
+        <v>0.7383</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4252</v>
+        <v>0.0171</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6932</v>
+        <v>0.7212</v>
       </c>
       <c r="V14" t="n">
         <v>2.1469</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7157</v>
+        <v>3.7491</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4534</v>
+        <v>2.5148</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2624</v>
+        <v>1.2343</v>
       </c>
       <c r="G15" t="n">
         <v>0.3525</v>
@@ -1624,13 +1624,13 @@
         <v>1.9838</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7167</v>
+        <v>1.7501</v>
       </c>
       <c r="T15" t="n">
-        <v>3.5201</v>
+        <v>1.5815</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1966</v>
+        <v>0.1686</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3373</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ALIAGA CHECA</t>
+          <t>L. SALA MAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6894</v>
+        <v>3.249</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1026</v>
+        <v>1.6793</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5868</v>
+        <v>1.5698</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3066</v>
+        <v>-0.3077</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9427</v>
+        <v>1.295</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6361</v>
+        <v>-1.6028</v>
       </c>
       <c r="J16" t="n">
-        <v>0.479</v>
+        <v>0.5285</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9985000000000001</v>
+        <v>2.1573</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5195</v>
+        <v>-1.6288</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1723</v>
+        <v>-0.8363</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0558</v>
+        <v>-0.8623</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1165</v>
+        <v>0.026</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7935</v>
+        <v>2.3806</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7855</v>
+        <v>2.3806</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5892</v>
+        <v>1.1762</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4091</v>
+        <v>1.1507</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1802</v>
+        <v>0.0254</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. SALA MAS</t>
+          <t>A. CUMELLES CESPEDES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3732</v>
+        <v>3.2486</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8833</v>
+        <v>3.0308</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4898</v>
+        <v>0.2177</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3077</v>
+        <v>2.012</v>
       </c>
       <c r="H17" t="n">
-        <v>1.295</v>
+        <v>2.8177</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6028</v>
+        <v>-0.8058</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5285</v>
+        <v>2.9187</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1573</v>
+        <v>3.4784</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.6288</v>
+        <v>-0.5597</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8363</v>
+        <v>-0.9067</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8623</v>
+        <v>-0.6607</v>
       </c>
       <c r="O17" t="n">
-        <v>0.026</v>
+        <v>-0.2461</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3806</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3806</v>
+        <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3003</v>
+        <v>0.6334</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3548</v>
+        <v>0.6236</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0545</v>
+        <v>0.0098</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CUMELLES CESPEDES</t>
+          <t>B. ENRICH TASIAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2427</v>
+        <v>2.6829</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9085</v>
+        <v>0.6217</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3342</v>
+        <v>2.0612</v>
       </c>
       <c r="G18" t="n">
-        <v>2.012</v>
+        <v>0.2541</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8177</v>
+        <v>-1.4211</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8058</v>
+        <v>1.6752</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9187</v>
+        <v>0.769</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4784</v>
+        <v>-1.1588</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5597</v>
+        <v>1.9278</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9067</v>
+        <v>-0.5149</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6607</v>
+        <v>-0.2623</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2461</v>
+        <v>-0.2526</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.3887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9838</v>
+        <v>2.3806</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3725</v>
+        <v>1.0402</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4988</v>
+        <v>0.8446</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1263</v>
+        <v>0.1955</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. BERNADÍ VALLS</t>
+          <t>M. ALIAGA CHECA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0991</v>
+        <v>2.5909</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8035</v>
+        <v>1.9802</v>
       </c>
       <c r="F19" t="n">
-        <v>3.9026</v>
+        <v>0.6106</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3484</v>
+        <v>0.3066</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.7605</v>
+        <v>0.9427</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4121</v>
+        <v>-0.6361</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.4433</v>
+        <v>0.479</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.5638</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1205</v>
+        <v>-0.5195</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0949</v>
+        <v>-0.1723</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1967</v>
+        <v>-0.0558</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2916</v>
+        <v>-0.1165</v>
       </c>
       <c r="P19" t="n">
         <v>0.7935</v>
@@ -1936,22 +1936,22 @@
         <v>1.7855</v>
       </c>
       <c r="S19" t="n">
-        <v>1.773</v>
+        <v>1.4907</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4252</v>
+        <v>1.2867</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3478</v>
+        <v>0.204</v>
       </c>
       <c r="V19" t="n">
-        <v>1.881</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>1.2065</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6745</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.9993</v>
+        <v>2.4414</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1952</v>
+        <v>0.1109</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1945</v>
+        <v>2.3305</v>
       </c>
       <c r="G20" t="n">
         <v>2.1434</v>
@@ -2014,13 +2014,13 @@
         <v>2.3806</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0623</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3797</v>
+        <v>-0.0736</v>
       </c>
       <c r="U20" t="n">
-        <v>0.442</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6032</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. ENRICH TASIAS</t>
+          <t>M. BERNADÍ VALLS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8719</v>
+        <v>1.2982</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9087</v>
+        <v>-2.2116</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7807</v>
+        <v>3.5098</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2541</v>
+        <v>-2.3484</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4211</v>
+        <v>-2.7605</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6752</v>
+        <v>0.4121</v>
       </c>
       <c r="J21" t="n">
-        <v>0.769</v>
+        <v>-2.4433</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1588</v>
+        <v>-2.5638</v>
       </c>
       <c r="L21" t="n">
-        <v>1.9278</v>
+        <v>0.1205</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5149</v>
+        <v>0.0949</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2623</v>
+        <v>-0.1967</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2526</v>
+        <v>0.2916</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3887</v>
+        <v>0.7935</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3806</v>
+        <v>1.7855</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7708</v>
+        <v>0.9721</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6858</v>
+        <v>0.0171</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.955</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.881</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. BENITO MULLERAT</t>
+          <t>S. QUINTANA CALVENTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4089</v>
+        <v>1.1479</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7269</v>
+        <v>-0.188</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1357</v>
+        <v>1.336</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7405</v>
+        <v>-0.419</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1511</v>
+        <v>-0.02</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5894</v>
+        <v>-0.3991</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1059</v>
+        <v>0.1452</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0537</v>
+        <v>0.9784</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1596</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6347</v>
+        <v>-0.5642</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2048</v>
+        <v>-0.9983</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5702</v>
+        <v>0.4341</v>
       </c>
       <c r="P22" t="n">
+        <v>-0.1984</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.9838</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.7855</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-0.9919</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.7774</v>
-      </c>
       <c r="S22" t="n">
-        <v>-0.3701</v>
+        <v>-0.3103</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6291</v>
+        <v>-0.425</v>
       </c>
       <c r="U22" t="n">
-        <v>0.259</v>
+        <v>0.1147</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.266</v>
+        <v>2.0757</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. QUINTANA CALVENTE</t>
+          <t>M. BENITO MULLERAT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.137</v>
+        <v>1.0695</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6982</v>
+        <v>-1.3187</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8352000000000001</v>
+        <v>2.3882</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.419</v>
+        <v>-0.7405</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.02</v>
+        <v>-0.1511</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3991</v>
+        <v>-0.5894</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1452</v>
+        <v>-0.1059</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9784</v>
+        <v>1.0537</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-1.1596</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5642</v>
+        <v>-0.6347</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9983</v>
+        <v>-1.2048</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4341</v>
+        <v>0.5702</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1984</v>
+        <v>1.7855</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7855</v>
+        <v>2.7774</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3212</v>
+        <v>0.2905</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9352</v>
+        <v>-0.2209</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3861</v>
+        <v>0.5115</v>
       </c>
       <c r="V23" t="n">
-        <v>2.0757</v>
+        <v>-0.266</v>
       </c>
       <c r="W23" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.9931</v>
+        <v>-0.8733</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4468</v>
+        <v>-1.2427</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4536</v>
+        <v>0.3695</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3909</v>
@@ -2326,13 +2326,13 @@
         <v>0.5952</v>
       </c>
       <c r="S24" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.1885</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.187</v>
+        <v>0.017</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2556</v>
+        <v>0.1714</v>
       </c>
       <c r="V24" t="n">
         <v>-0.266</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>26.5219</v>
+        <v>27.2019</v>
       </c>
       <c r="E25" t="n">
-        <v>8.301600000000001</v>
+        <v>8.301700000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>18.2202</v>
+        <v>18.9004</v>
       </c>
       <c r="G25" t="n">
         <v>1.5907</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2300999999999997</v>
+        <v>0.2301</v>
       </c>
       <c r="I25" t="n">
-        <v>1.360299999999999</v>
+        <v>1.3603</v>
       </c>
       <c r="J25" t="n">
         <v>6.3058</v>
@@ -2383,7 +2383,7 @@
         <v>6.5332</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.2274999999999998</v>
+        <v>-0.2275</v>
       </c>
       <c r="M25" t="n">
         <v>-4.715199999999999</v>
@@ -2404,13 +2404,13 @@
         <v>21.8223</v>
       </c>
       <c r="S25" t="n">
-        <v>7.793899999999998</v>
+        <v>8.4742</v>
       </c>
       <c r="T25" t="n">
-        <v>4.818799999999999</v>
+        <v>4.8188</v>
       </c>
       <c r="U25" t="n">
-        <v>2.9751</v>
+        <v>3.6552</v>
       </c>
       <c r="V25" t="n">
         <v>5.234299999999999</v>
